--- a/Tipos de trabajo/output/resumen_trabajos.xlsx
+++ b/Tipos de trabajo/output/resumen_trabajos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/Tipos de trabajo/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0F901F8-6BB6-9F41-ACAA-F6183F1F3515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6495492-A208-EE48-8B30-3982E9824317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="20400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="trabajos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="18" r:id="rId3"/>
+    <pivotCache cacheId="132" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3755" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3801" uniqueCount="1151">
   <si>
     <t>Técnico</t>
   </si>
@@ -4322,6 +4322,44 @@
   </si>
   <si>
     <t>Cuenta de OT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizo visita con don Nicolas Valenzuela de anglo American para revisión de carro galileo, se encuentra caudalimetro no invasivo descalibrado, se retira y se envía a calibración por garantía. </t>
+  </si>
+  <si>
+    <t>Calidad del Aire</t>
+  </si>
+  <si>
+    <t>[Calidad del Aire] Estación Veta Blanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se procede ir al punto para revisión e inspección visual en compañía de don Nicolas Valenzuela,  lo que provoca fallas de medición es la ventosa del lugar que se encuentra restringida su válvula, además se procede a realizar reemplazo de tarjeta SD del tablero. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levantar punto Viñas de concha y toro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">En Viñas concha y toro se monta placa modbus en mag6000 queda leyendo equipo, se valida dato de terreno con plataforma.
+E. Biodiversa planta se realizan pruebas de control y de lectura modbus de vdf ksb.
+</t>
+  </si>
+  <si>
+    <t>PH de entrada en planta Biodiversa zona 1 esta desconectado del equipo, por ende marca dato erroneo.
+En planta Biodiversa vdf ksb pantalla no enciende, voltimetro marca más de 500v puede que el equipo falle lo que provocaría perdida de lecturas modbus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por aviso de oficina procedemos ir al punto a recetear el tablero ya que se encontraba la sonda dando datos erróneo. </t>
+  </si>
+  <si>
+    <t>Pozos monitoreo exteriores y ET 0F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realizo inspección visual de cada punto para que no se encontrarán bandalizado o con algún problema. </t>
+  </si>
+  <si>
+    <t>Se da revisión al punto por que ese encontraba caído y dando datos erróneos la sonda. 
+Se deja sonda con agua ya que se encontraba sin agua.
+Válvula estaba abierta. Habían indicios qué el agua había corrido por el piso hacia el exterior.</t>
   </si>
 </sst>
 </file>
@@ -4382,7 +4420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4391,15 +4429,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4544,9 +4576,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:lumMod val="60000"/>
-            </a:schemeClr>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -4607,7 +4637,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -4729,7 +4759,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -4790,7 +4820,7 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent4"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -4851,7 +4881,7 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent5"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -4912,7 +4942,7 @@
         <c:idx val="7"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent6"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -13452,7 +13482,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE53494B-13EC-3446-A147-8F63BBA3D585}" name="Resumen" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DE53494B-13EC-3446-A147-8F63BBA3D585}" name="Resumen" cacheId="132" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A1:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13934,7 +13964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N457"/>
+  <dimension ref="A1:N463"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -13952,31 +13982,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="2" t="s">
         <v>1107</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -29413,336 +29443,304 @@
       </c>
     </row>
     <row r="434" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A434" s="4">
+      <c r="A434">
         <v>336</v>
       </c>
-      <c r="B434" s="4" t="s">
+      <c r="B434" t="s">
         <v>67</v>
       </c>
-      <c r="C434" s="4" t="s">
+      <c r="C434" t="s">
         <v>1105</v>
       </c>
-      <c r="D434" s="4" t="s">
+      <c r="D434" t="s">
         <v>69</v>
       </c>
-      <c r="E434" s="4" t="s">
+      <c r="E434" t="s">
         <v>147</v>
       </c>
-      <c r="F434" s="4" t="s">
+      <c r="F434" t="s">
         <v>17</v>
       </c>
-      <c r="G434" s="5">
+      <c r="G434" s="1">
         <v>46007</v>
       </c>
-      <c r="H434" s="4" t="s">
+      <c r="H434" t="s">
         <v>479</v>
       </c>
-      <c r="I434" s="4" t="s">
+      <c r="I434" t="s">
         <v>1106</v>
       </c>
-      <c r="J434" s="4">
-        <v>5</v>
-      </c>
-      <c r="K434" s="4"/>
-      <c r="L434" s="4"/>
-      <c r="M434" s="4"/>
-      <c r="N434" s="4"/>
+      <c r="J434">
+        <v>5</v>
+      </c>
     </row>
     <row r="435" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A435" s="4">
+      <c r="A435">
         <v>337</v>
       </c>
-      <c r="B435" s="4" t="s">
+      <c r="B435" t="s">
         <v>113</v>
       </c>
-      <c r="C435" s="4" t="s">
+      <c r="C435" t="s">
         <v>1102</v>
       </c>
-      <c r="D435" s="4" t="s">
+      <c r="D435" t="s">
         <v>63</v>
       </c>
-      <c r="E435" s="4" t="s">
+      <c r="E435" t="s">
         <v>1103</v>
       </c>
-      <c r="F435" s="4" t="s">
+      <c r="F435" t="s">
         <v>227</v>
       </c>
-      <c r="G435" s="5">
+      <c r="G435" s="1">
         <v>46008</v>
       </c>
-      <c r="H435" s="4" t="s">
+      <c r="H435" t="s">
         <v>479</v>
       </c>
-      <c r="I435" s="4" t="s">
+      <c r="I435" t="s">
         <v>1104</v>
       </c>
-      <c r="J435" s="4">
-        <v>5</v>
-      </c>
-      <c r="K435" s="4" t="s">
+      <c r="J435">
+        <v>5</v>
+      </c>
+      <c r="K435" t="s">
         <v>209</v>
       </c>
-      <c r="L435" s="4" t="s">
+      <c r="L435" t="s">
         <v>321</v>
       </c>
-      <c r="M435" s="4" t="s">
+      <c r="M435" t="s">
         <v>321</v>
       </c>
-      <c r="N435" s="4" t="s">
+      <c r="N435" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="436" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A436" s="4">
+      <c r="A436">
         <v>338</v>
       </c>
-      <c r="B436" s="4" t="s">
+      <c r="B436" t="s">
         <v>13</v>
       </c>
-      <c r="C436" s="4" t="s">
+      <c r="C436" t="s">
         <v>296</v>
       </c>
-      <c r="D436" s="4" t="s">
+      <c r="D436" t="s">
         <v>15</v>
       </c>
-      <c r="E436" s="4" t="s">
+      <c r="E436" t="s">
         <v>177</v>
       </c>
-      <c r="F436" s="4" t="s">
+      <c r="F436" t="s">
         <v>17</v>
       </c>
-      <c r="G436" s="5">
+      <c r="G436" s="1">
         <v>46007</v>
       </c>
-      <c r="H436" s="4" t="s">
+      <c r="H436" t="s">
         <v>134</v>
       </c>
-      <c r="I436" s="4" t="s">
+      <c r="I436" t="s">
         <v>1101</v>
       </c>
-      <c r="J436" s="4">
-        <v>5</v>
-      </c>
-      <c r="K436" s="4"/>
-      <c r="L436" s="4"/>
-      <c r="M436" s="4"/>
-      <c r="N436" s="4"/>
+      <c r="J436">
+        <v>5</v>
+      </c>
     </row>
     <row r="437" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A437" s="4">
+      <c r="A437">
         <v>339</v>
       </c>
-      <c r="B437" s="4" t="s">
+      <c r="B437" t="s">
         <v>13</v>
       </c>
-      <c r="C437" s="4" t="s">
+      <c r="C437" t="s">
         <v>1097</v>
       </c>
-      <c r="D437" s="4" t="s">
+      <c r="D437" t="s">
         <v>15</v>
       </c>
-      <c r="E437" s="4" t="s">
+      <c r="E437" t="s">
         <v>900</v>
       </c>
-      <c r="F437" s="4" t="s">
+      <c r="F437" t="s">
         <v>17</v>
       </c>
-      <c r="G437" s="5">
+      <c r="G437" s="1">
         <v>46008</v>
       </c>
-      <c r="H437" s="4" t="s">
+      <c r="H437" t="s">
         <v>134</v>
       </c>
-      <c r="I437" s="4" t="s">
+      <c r="I437" t="s">
         <v>1098</v>
       </c>
-      <c r="J437" s="4">
-        <v>5</v>
-      </c>
-      <c r="K437" s="4"/>
-      <c r="L437" s="4"/>
-      <c r="M437" s="4"/>
-      <c r="N437" s="4"/>
+      <c r="J437">
+        <v>5</v>
+      </c>
     </row>
     <row r="438" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A438" s="4">
+      <c r="A438">
         <v>339</v>
       </c>
-      <c r="B438" s="4" t="s">
+      <c r="B438" t="s">
         <v>13</v>
       </c>
-      <c r="C438" s="4" t="s">
+      <c r="C438" t="s">
         <v>1097</v>
       </c>
-      <c r="D438" s="4" t="s">
+      <c r="D438" t="s">
         <v>15</v>
       </c>
-      <c r="E438" s="4" t="s">
+      <c r="E438" t="s">
         <v>1099</v>
       </c>
-      <c r="F438" s="4" t="s">
+      <c r="F438" t="s">
         <v>17</v>
       </c>
-      <c r="G438" s="5">
+      <c r="G438" s="1">
         <v>46008</v>
       </c>
-      <c r="H438" s="4" t="s">
+      <c r="H438" t="s">
         <v>134</v>
       </c>
-      <c r="I438" s="4" t="s">
+      <c r="I438" t="s">
         <v>1100</v>
       </c>
-      <c r="J438" s="4">
-        <v>5</v>
-      </c>
-      <c r="K438" s="4"/>
-      <c r="L438" s="4"/>
-      <c r="M438" s="4"/>
-      <c r="N438" s="4"/>
+      <c r="J438">
+        <v>5</v>
+      </c>
     </row>
     <row r="439" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A439" s="4">
+      <c r="A439">
         <v>340</v>
       </c>
-      <c r="B439" s="4" t="s">
+      <c r="B439" t="s">
         <v>67</v>
       </c>
-      <c r="C439" s="4" t="s">
+      <c r="C439" t="s">
         <v>1095</v>
       </c>
-      <c r="D439" s="4" t="s">
+      <c r="D439" t="s">
         <v>69</v>
       </c>
-      <c r="E439" s="4" t="s">
+      <c r="E439" t="s">
         <v>147</v>
       </c>
-      <c r="F439" s="4" t="s">
+      <c r="F439" t="s">
         <v>17</v>
       </c>
-      <c r="G439" s="5">
+      <c r="G439" s="1">
         <v>46008</v>
       </c>
-      <c r="H439" s="4" t="s">
+      <c r="H439" t="s">
         <v>71</v>
       </c>
-      <c r="I439" s="4" t="s">
+      <c r="I439" t="s">
         <v>1096</v>
       </c>
-      <c r="J439" s="4">
-        <v>5</v>
-      </c>
-      <c r="K439" s="4"/>
-      <c r="L439" s="4"/>
-      <c r="M439" s="4"/>
-      <c r="N439" s="4"/>
+      <c r="J439">
+        <v>5</v>
+      </c>
     </row>
     <row r="440" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A440" s="4">
+      <c r="A440">
         <v>341</v>
       </c>
-      <c r="B440" s="4" t="s">
+      <c r="B440" t="s">
         <v>67</v>
       </c>
-      <c r="C440" s="4" t="s">
+      <c r="C440" t="s">
         <v>1093</v>
       </c>
-      <c r="D440" s="4" t="s">
+      <c r="D440" t="s">
         <v>69</v>
       </c>
-      <c r="E440" s="4" t="s">
+      <c r="E440" t="s">
         <v>147</v>
       </c>
-      <c r="F440" s="4" t="s">
+      <c r="F440" t="s">
         <v>17</v>
       </c>
-      <c r="G440" s="5">
+      <c r="G440" s="1">
         <v>46009</v>
       </c>
-      <c r="H440" s="4" t="s">
+      <c r="H440" t="s">
         <v>479</v>
       </c>
-      <c r="I440" s="4" t="s">
+      <c r="I440" t="s">
         <v>1094</v>
       </c>
-      <c r="J440" s="4">
-        <v>5</v>
-      </c>
-      <c r="K440" s="4"/>
-      <c r="L440" s="4"/>
-      <c r="M440" s="4"/>
-      <c r="N440" s="4"/>
+      <c r="J440">
+        <v>5</v>
+      </c>
     </row>
     <row r="441" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A441" s="4">
+      <c r="A441">
         <v>342</v>
       </c>
-      <c r="B441" s="4" t="s">
+      <c r="B441" t="s">
         <v>13</v>
       </c>
-      <c r="C441" s="4" t="s">
+      <c r="C441" t="s">
         <v>1090</v>
       </c>
-      <c r="D441" s="4" t="s">
+      <c r="D441" t="s">
         <v>15</v>
       </c>
-      <c r="E441" s="4" t="s">
+      <c r="E441" t="s">
         <v>1088</v>
       </c>
-      <c r="F441" s="4" t="s">
+      <c r="F441" t="s">
         <v>17</v>
       </c>
-      <c r="G441" s="5">
+      <c r="G441" s="1">
         <v>46010</v>
       </c>
-      <c r="H441" s="4" t="s">
+      <c r="H441" t="s">
         <v>134</v>
       </c>
-      <c r="I441" s="4" t="s">
+      <c r="I441" t="s">
         <v>1091</v>
       </c>
-      <c r="J441" s="4">
-        <v>5</v>
-      </c>
-      <c r="K441" s="4"/>
-      <c r="L441" s="4"/>
-      <c r="M441" s="4"/>
-      <c r="N441" s="4"/>
+      <c r="J441">
+        <v>5</v>
+      </c>
     </row>
     <row r="442" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A442" s="4">
+      <c r="A442">
         <v>342</v>
       </c>
-      <c r="B442" s="4" t="s">
+      <c r="B442" t="s">
         <v>13</v>
       </c>
-      <c r="C442" s="4" t="s">
+      <c r="C442" t="s">
         <v>1090</v>
       </c>
-      <c r="D442" s="4" t="s">
+      <c r="D442" t="s">
         <v>15</v>
       </c>
-      <c r="E442" s="4" t="s">
+      <c r="E442" t="s">
         <v>897</v>
       </c>
-      <c r="F442" s="4" t="s">
+      <c r="F442" t="s">
         <v>17</v>
       </c>
-      <c r="G442" s="5">
+      <c r="G442" s="1">
         <v>46010</v>
       </c>
-      <c r="H442" s="4" t="s">
+      <c r="H442" t="s">
         <v>134</v>
       </c>
-      <c r="I442" s="4" t="s">
+      <c r="I442" t="s">
         <v>1092</v>
       </c>
-      <c r="J442" s="4">
-        <v>5</v>
-      </c>
-      <c r="K442" s="4"/>
-      <c r="L442" s="4"/>
-      <c r="M442" s="4"/>
-      <c r="N442" s="4"/>
+      <c r="J442">
+        <v>5</v>
+      </c>
     </row>
     <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443">
@@ -30234,6 +30232,210 @@
       </c>
       <c r="N457" t="s">
         <v>1136</v>
+      </c>
+    </row>
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A458">
+        <v>361</v>
+      </c>
+      <c r="B458" t="s">
+        <v>132</v>
+      </c>
+      <c r="C458" t="s">
+        <v>50</v>
+      </c>
+      <c r="D458" t="s">
+        <v>199</v>
+      </c>
+      <c r="E458" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F458" t="s">
+        <v>17</v>
+      </c>
+      <c r="G458" s="1">
+        <v>46021</v>
+      </c>
+      <c r="H458" t="s">
+        <v>710</v>
+      </c>
+      <c r="I458" t="s">
+        <v>1140</v>
+      </c>
+      <c r="J458">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A459">
+        <v>361</v>
+      </c>
+      <c r="B459" t="s">
+        <v>132</v>
+      </c>
+      <c r="C459" t="s">
+        <v>50</v>
+      </c>
+      <c r="D459" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E459" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F459" t="s">
+        <v>17</v>
+      </c>
+      <c r="G459" s="1">
+        <v>46021</v>
+      </c>
+      <c r="H459" t="s">
+        <v>710</v>
+      </c>
+      <c r="I459" t="s">
+        <v>1143</v>
+      </c>
+      <c r="J459">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A460">
+        <v>362</v>
+      </c>
+      <c r="B460" t="s">
+        <v>113</v>
+      </c>
+      <c r="C460" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D460" t="s">
+        <v>554</v>
+      </c>
+      <c r="E460" t="s">
+        <v>555</v>
+      </c>
+      <c r="F460" t="s">
+        <v>227</v>
+      </c>
+      <c r="G460" s="1">
+        <v>46021</v>
+      </c>
+      <c r="H460" t="s">
+        <v>556</v>
+      </c>
+      <c r="I460" t="s">
+        <v>1145</v>
+      </c>
+      <c r="J460">
+        <v>5</v>
+      </c>
+      <c r="K460" t="s">
+        <v>209</v>
+      </c>
+      <c r="L460" t="s">
+        <v>321</v>
+      </c>
+      <c r="M460" t="s">
+        <v>321</v>
+      </c>
+      <c r="N460" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="461" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A461">
+        <v>365</v>
+      </c>
+      <c r="B461" t="s">
+        <v>132</v>
+      </c>
+      <c r="C461" t="s">
+        <v>50</v>
+      </c>
+      <c r="D461" t="s">
+        <v>15</v>
+      </c>
+      <c r="E461" t="s">
+        <v>323</v>
+      </c>
+      <c r="F461" t="s">
+        <v>17</v>
+      </c>
+      <c r="G461" s="1">
+        <v>46022</v>
+      </c>
+      <c r="H461" t="s">
+        <v>710</v>
+      </c>
+      <c r="I461" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J461">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A462">
+        <v>365</v>
+      </c>
+      <c r="B462" t="s">
+        <v>132</v>
+      </c>
+      <c r="C462" t="s">
+        <v>50</v>
+      </c>
+      <c r="D462" t="s">
+        <v>199</v>
+      </c>
+      <c r="E462" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F462" t="s">
+        <v>17</v>
+      </c>
+      <c r="G462" s="1">
+        <v>46022</v>
+      </c>
+      <c r="H462" t="s">
+        <v>710</v>
+      </c>
+      <c r="I462" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J462">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="463" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A463">
+        <v>365</v>
+      </c>
+      <c r="B463" t="s">
+        <v>132</v>
+      </c>
+      <c r="C463" t="s">
+        <v>50</v>
+      </c>
+      <c r="D463" t="s">
+        <v>15</v>
+      </c>
+      <c r="E463" t="s">
+        <v>516</v>
+      </c>
+      <c r="F463" t="s">
+        <v>17</v>
+      </c>
+      <c r="G463" s="1">
+        <v>46022</v>
+      </c>
+      <c r="H463" t="s">
+        <v>710</v>
+      </c>
+      <c r="I463" t="s">
+        <v>1150</v>
+      </c>
+      <c r="J463">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -30255,7 +30457,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="B1" t="s">
@@ -30263,66 +30465,66 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>456</v>
       </c>
     </row>

--- a/Tipos de trabajo/output/resumen_trabajos.xlsx
+++ b/Tipos de trabajo/output/resumen_trabajos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/Tipos de trabajo/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57060C91-9467-934D-9D2F-72B7265D839F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4885F51A-AECB-BD41-B80E-C050331128FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-5560" windowWidth="33720" windowHeight="19920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37540" yWindow="-5520" windowWidth="33720" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="trabajos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="226" r:id="rId3"/>
+    <pivotCache cacheId="258" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3865" uniqueCount="1178">
   <si>
     <t>Técnico</t>
   </si>
@@ -4399,6 +4399,56 @@
 - Se hace entrega de documentación a Sr. Nicolas solicitado por Rodrigo López.
 - Se espero a don Diego Ramos para la verificación de instalación de los postes en los puntos PEM, pero no fue posible reunirnos, esta coordinado para hoy a las 10:00hrs apox.
 - Se rotula las herramientas acorde al color reactivo de este mes. </t>
+  </si>
+  <si>
+    <t>Configuración telemetria pozo BN12</t>
+  </si>
+  <si>
+    <t>Se intstala sensor de nivel en pozo y se configura el equipo junto con el flujometro a traves de lecturas modbus, se comprueban valores en PLC.
+Por otro lado se configura la comunicación del punto a la telemetria WeTechs para la visualizacion de datos.
+Adicionalmente se instalan equipos de comunicación para la lectura de datos a través de red LORA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migración a Red Lora Wan LT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matias Signorio - Paula Riquelme </t>
+  </si>
+  <si>
+    <t>Se instalan y configuración dispositivo red Lora Wan, se validan datos terreno plataforma ok + antena ok.</t>
+  </si>
+  <si>
+    <t>Uc300-915M</t>
+  </si>
+  <si>
+    <t>6445F17824030004</t>
+  </si>
+  <si>
+    <t>Punto ok.</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN1</t>
+  </si>
+  <si>
+    <t>Se instalan y configuración dispositivo red Lora Wan, se validan datos terreno plataforma ok. + antena</t>
+  </si>
+  <si>
+    <t>6445F15707350005</t>
+  </si>
+  <si>
+    <t>Punto transmisión de datos ok.</t>
+  </si>
+  <si>
+    <t>Se instalan y configuración dispositivo red Lora Wan, se validan datos terreno plataforma ok. + antena ok.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uc300-915M </t>
+  </si>
+  <si>
+    <t>6445F15534110005</t>
+  </si>
+  <si>
+    <t>Punto con transmisión de datos ok.</t>
   </si>
 </sst>
 </file>
@@ -4459,7 +4509,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4472,7 +4522,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13618,7 +13667,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58C144FF-F8BA-0042-8CC8-638EF8B29700}" name="Resumen" cacheId="226" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58C144FF-F8BA-0042-8CC8-638EF8B29700}" name="Resumen" cacheId="258" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A1:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13790,14 +13839,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}" name="Tabla1" displayName="Tabla1" ref="A1:N466" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:N466" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}">
-    <filterColumn colId="6">
-      <filters>
-        <dateGroupItem year="2025" dateTimeGrouping="year"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}" name="Tabla1" displayName="Tabla1" ref="A1:N470" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:N470" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:N422">
     <sortCondition descending="1" ref="E1:E466"/>
   </sortState>
@@ -14106,7 +14149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N466"/>
+  <dimension ref="A1:N470"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -30580,7 +30623,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:14" hidden="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>366</v>
       </c>
@@ -30621,7 +30664,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="465" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>368</v>
       </c>
@@ -30653,7 +30696,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>368</v>
       </c>
@@ -30683,6 +30726,170 @@
       </c>
       <c r="J466">
         <v>5</v>
+      </c>
+    </row>
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A467">
+        <v>369</v>
+      </c>
+      <c r="B467" t="s">
+        <v>67</v>
+      </c>
+      <c r="C467" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D467" t="s">
+        <v>63</v>
+      </c>
+      <c r="E467" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F467" t="s">
+        <v>17</v>
+      </c>
+      <c r="G467" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H467" t="s">
+        <v>479</v>
+      </c>
+      <c r="I467" t="s">
+        <v>1163</v>
+      </c>
+      <c r="J467">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A468">
+        <v>370</v>
+      </c>
+      <c r="B468" t="s">
+        <v>113</v>
+      </c>
+      <c r="C468" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D468" t="s">
+        <v>63</v>
+      </c>
+      <c r="E468" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F468" t="s">
+        <v>227</v>
+      </c>
+      <c r="G468" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H468" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I468" t="s">
+        <v>1166</v>
+      </c>
+      <c r="J468">
+        <v>5</v>
+      </c>
+      <c r="K468" t="s">
+        <v>209</v>
+      </c>
+      <c r="L468" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M468" t="s">
+        <v>1168</v>
+      </c>
+      <c r="N468" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A469">
+        <v>370</v>
+      </c>
+      <c r="B469" t="s">
+        <v>113</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D469" t="s">
+        <v>63</v>
+      </c>
+      <c r="E469" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F469" t="s">
+        <v>227</v>
+      </c>
+      <c r="G469" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H469" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I469" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J469">
+        <v>5</v>
+      </c>
+      <c r="K469" t="s">
+        <v>209</v>
+      </c>
+      <c r="L469" t="s">
+        <v>1167</v>
+      </c>
+      <c r="M469" t="s">
+        <v>1172</v>
+      </c>
+      <c r="N469" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A470">
+        <v>370</v>
+      </c>
+      <c r="B470" t="s">
+        <v>113</v>
+      </c>
+      <c r="C470" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D470" t="s">
+        <v>63</v>
+      </c>
+      <c r="E470" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F470" t="s">
+        <v>227</v>
+      </c>
+      <c r="G470" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H470" t="s">
+        <v>1165</v>
+      </c>
+      <c r="I470" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J470">
+        <v>5</v>
+      </c>
+      <c r="K470" t="s">
+        <v>209</v>
+      </c>
+      <c r="L470" t="s">
+        <v>1175</v>
+      </c>
+      <c r="M470" t="s">
+        <v>1176</v>
+      </c>
+      <c r="N470" t="s">
+        <v>1177</v>
       </c>
     </row>
   </sheetData>
@@ -30715,7 +30922,7 @@
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>14</v>
       </c>
     </row>
@@ -30723,7 +30930,7 @@
       <c r="A3" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>4</v>
       </c>
     </row>
@@ -30731,7 +30938,7 @@
       <c r="A4" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>94</v>
       </c>
     </row>
@@ -30739,7 +30946,7 @@
       <c r="A5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>50</v>
       </c>
     </row>
@@ -30747,7 +30954,7 @@
       <c r="A6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>20</v>
       </c>
     </row>
@@ -30755,7 +30962,7 @@
       <c r="A7" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>33</v>
       </c>
     </row>
@@ -30763,7 +30970,7 @@
       <c r="A8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>247</v>
       </c>
     </row>
@@ -30771,7 +30978,7 @@
       <c r="A9" s="5" t="s">
         <v>1138</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>462</v>
       </c>
     </row>

--- a/Tipos de trabajo/output/resumen_trabajos.xlsx
+++ b/Tipos de trabajo/output/resumen_trabajos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/Tipos de trabajo/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4885F51A-AECB-BD41-B80E-C050331128FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721C2010-4C51-C545-99A7-D67E1DFF8B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37540" yWindow="-5520" windowWidth="33720" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35500" yWindow="-4940" windowWidth="33740" windowHeight="19940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="trabajos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="258" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3865" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="1214">
   <si>
     <t>Técnico</t>
   </si>
@@ -4449,6 +4449,147 @@
   </si>
   <si>
     <t>Punto con transmisión de datos ok.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visita a Pem 01 con SS
+Se debe entregar a SS estructura de soporte para panel
+ dimensiones : 1217*992*35mm
+Se acude para verificar el posicionamiento del poste a instalar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visita a Pem 03 con SS
+Se debe entregar a SS estructura de soporte para panel y un panel solar, ya que fue vandalizado. 
+ dimensiones panel : 1217*992*35mm
+Se acude para verificar el posicionamiento del poste a instalar. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Válvula desde piscina UG hacia piscina 3800 </t>
+  </si>
+  <si>
+    <t>Se acude al punto para cerrar válvula por completo por solicitud del cliente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza limpieza de los tableros, reapriete de terminales, mediciones de voltaje, sopletiado, limpieza de panel fotovoltaico, revisión de software ecostruxture y toolbox, verificación y contratación de variables en plataforma, limpieza de sonda multiparamétrica y sensor hidrostatico. </t>
+  </si>
+  <si>
+    <t>1 tablero fotovoltaico + uc300
+1 tablero PLC 16R</t>
+  </si>
+  <si>
+    <t>Falta rotular tableros con código qr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panel fotovoltaico </t>
+  </si>
+  <si>
+    <t xml:space="preserve">... </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza la limpieza de panel fotovoltaico 
+No presenta observaciones
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude al punto para resolución de ticket, ya que presentaba peaks de valores respecto a la conductividaddel agua en plataforma.
+Se revisan software y se verifica la lectura
+Se encuentra en orden y registrando valores en plataforma. </t>
+  </si>
+  <si>
+    <t>- Tablero PLC 16R
+- Tablero fotovoltaico + UC300</t>
+  </si>
+  <si>
+    <t>Panel fotovoltsico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza limpieza
+No presenta observaciones </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garantía pantalla sala de control </t>
+  </si>
+  <si>
+    <t>Sala de control LPG</t>
+  </si>
+  <si>
+    <t>Hernan Rojas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza instalación de nueva pantalla por garantia </t>
+  </si>
+  <si>
+    <t>Thinkpad lenovo</t>
+  </si>
+  <si>
+    <t>V30F882K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposición pantalla dañada </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se realiza limpieza de tableros, limpieza de panel fotovoltaico, reapriete de terminales, mediciones de voltaje, revisión, contratación y validación de datos en plataforma y software ecostruxture.
+Datos congruentes. 
+</t>
+  </si>
+  <si>
+    <t>Tablero de banco baterias
+Tablero We connect
+Tablero PLC16R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No presenta observaciones </t>
+  </si>
+  <si>
+    <t>Mantenimiento correctivo R2700</t>
+  </si>
+  <si>
+    <t>En la visita a terreno se constata que la caida de la telemetria se debe a la desnergizacion de antena starlink, esto ultimo por activación de interruptor automático.
+Se regulariza la condición y adicionalmente se integra la UPS al circuito de alimentación conectando entrada en tablero de paso existente y su salida aguas arriba a automático general telemetría. 
+De esta forma si la red electerica cae, la UPS continuará entregandole energia al sistema completo, una vez la UPS se agote, el inversor continua alimentando con baterias y solución solar.
+Queda pendiente en sala R2700 instalar gabinete para remontar 2 baterias de 100AH y conectarlas al sistema de respaldo.
+Instalación de conectores MC4 paralelo para regularizar la conexión fisica de los paneles.
+Instalar automático DC para la protección de banco de baterías.
+Regularizar terminales en cables de alimentación solar y baterías (requiere ferrules) cable 6AWG.</t>
+  </si>
+  <si>
+    <t>Implementacion red LORA WAN</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo BN4</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.
+Queda pendiente validación de datos ya que punto se encuentra desnergizado.</t>
+  </si>
+  <si>
+    <t>[Global Tórtolas] Pozo O4</t>
+  </si>
+  <si>
+    <t>Se instala equipos y antena para monitoreo de datos a través de red lora con éxito.
+Queda pendiente validación de datos ya que punto se encuentra desnergizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planta Solar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude a revisión de los pozos de inyección del 17 al 20.
+Se contrasta Caudal en terreno y en plataforma siendo estos 4 puntos coherentes y valores correctos
+Se revisa planta Solar y se limpian paneles para evitar algún tipo de falla respectivamente.
+Observaciones
+PI-17 se destraba válvula vortex y continua su funcionamiento normal.
+</t>
+  </si>
+  <si>
+    <t>[APR Los Caleos] Pozo 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se acude a revisar el pozo 4 de los caleos por la falla que tuvo el día de ayer, hablamos con el operador y comento que hoy le paso algo parecido y volvió la señal, también hace unas semanas en un turno de noche como 3 veces. Asique fuimos al punto con el para ver la situación 
+- Tablero We connect presenta muy alta temperatura en teltonika y en el tablero en general, tablero no cuenta con ventilación 
+- Fuente de voltaje estaba en 28,40v se reduce a 26,20, por sobrecalentamiento, se observa que potenciómetro de voltaje de la fuente esta hundido hacia dentro y se hace difícil regular.
+Son indicios para pensar en reemplazar la fuente y quizás una mejora en sentido de ventilación o enfriamiento del tablero. </t>
   </si>
 </sst>
 </file>
@@ -13667,7 +13808,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58C144FF-F8BA-0042-8CC8-638EF8B29700}" name="Resumen" cacheId="258" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58C144FF-F8BA-0042-8CC8-638EF8B29700}" name="Resumen" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A1:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -13839,8 +13980,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}" name="Tabla1" displayName="Tabla1" ref="A1:N470" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:N470" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}" name="Tabla1" displayName="Tabla1" ref="A1:N489" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:N489" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:N422">
     <sortCondition descending="1" ref="E1:E466"/>
   </sortState>
@@ -14149,7 +14290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N470"/>
+  <dimension ref="A1:N489"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -30890,6 +31031,695 @@
       </c>
       <c r="N470" t="s">
         <v>1177</v>
+      </c>
+    </row>
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A471">
+        <v>372</v>
+      </c>
+      <c r="B471" t="s">
+        <v>13</v>
+      </c>
+      <c r="C471" t="s">
+        <v>50</v>
+      </c>
+      <c r="D471" t="s">
+        <v>15</v>
+      </c>
+      <c r="E471" t="s">
+        <v>136</v>
+      </c>
+      <c r="F471" t="s">
+        <v>47</v>
+      </c>
+      <c r="G471" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H471" t="s">
+        <v>134</v>
+      </c>
+      <c r="I471" t="s">
+        <v>1178</v>
+      </c>
+      <c r="J471">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A472">
+        <v>372</v>
+      </c>
+      <c r="B472" t="s">
+        <v>13</v>
+      </c>
+      <c r="C472" t="s">
+        <v>50</v>
+      </c>
+      <c r="D472" t="s">
+        <v>15</v>
+      </c>
+      <c r="E472" t="s">
+        <v>174</v>
+      </c>
+      <c r="F472" t="s">
+        <v>47</v>
+      </c>
+      <c r="G472" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H472" t="s">
+        <v>134</v>
+      </c>
+      <c r="I472" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J472">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A473">
+        <v>372</v>
+      </c>
+      <c r="B473" t="s">
+        <v>13</v>
+      </c>
+      <c r="C473" t="s">
+        <v>50</v>
+      </c>
+      <c r="D473" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E473" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F473" t="s">
+        <v>17</v>
+      </c>
+      <c r="G473" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H473" t="s">
+        <v>134</v>
+      </c>
+      <c r="I473" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J473">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A474">
+        <v>372</v>
+      </c>
+      <c r="B474" t="s">
+        <v>13</v>
+      </c>
+      <c r="C474" t="s">
+        <v>50</v>
+      </c>
+      <c r="D474" t="s">
+        <v>15</v>
+      </c>
+      <c r="E474" t="s">
+        <v>564</v>
+      </c>
+      <c r="F474" t="s">
+        <v>217</v>
+      </c>
+      <c r="G474" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H474" t="s">
+        <v>134</v>
+      </c>
+      <c r="I474" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J474">
+        <v>5</v>
+      </c>
+      <c r="K474" t="s">
+        <v>221</v>
+      </c>
+      <c r="L474" t="s">
+        <v>1183</v>
+      </c>
+      <c r="M474" t="s">
+        <v>211</v>
+      </c>
+      <c r="N474" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A475">
+        <v>372</v>
+      </c>
+      <c r="B475" t="s">
+        <v>13</v>
+      </c>
+      <c r="C475" t="s">
+        <v>50</v>
+      </c>
+      <c r="D475" t="s">
+        <v>15</v>
+      </c>
+      <c r="E475" t="s">
+        <v>564</v>
+      </c>
+      <c r="F475" t="s">
+        <v>217</v>
+      </c>
+      <c r="G475" s="1">
+        <v>46028</v>
+      </c>
+      <c r="H475" t="s">
+        <v>134</v>
+      </c>
+      <c r="I475" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J475">
+        <v>5</v>
+      </c>
+      <c r="K475" t="s">
+        <v>209</v>
+      </c>
+      <c r="L475" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M475" t="s">
+        <v>1186</v>
+      </c>
+      <c r="N475" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A476">
+        <v>373</v>
+      </c>
+      <c r="B476" t="s">
+        <v>13</v>
+      </c>
+      <c r="C476" t="s">
+        <v>50</v>
+      </c>
+      <c r="D476" t="s">
+        <v>15</v>
+      </c>
+      <c r="E476" t="s">
+        <v>323</v>
+      </c>
+      <c r="F476" t="s">
+        <v>17</v>
+      </c>
+      <c r="G476" s="1">
+        <v>46029</v>
+      </c>
+      <c r="H476" t="s">
+        <v>134</v>
+      </c>
+      <c r="I476" t="s">
+        <v>1188</v>
+      </c>
+      <c r="J476">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A477">
+        <v>373</v>
+      </c>
+      <c r="B477" t="s">
+        <v>13</v>
+      </c>
+      <c r="C477" t="s">
+        <v>50</v>
+      </c>
+      <c r="D477" t="s">
+        <v>15</v>
+      </c>
+      <c r="E477" t="s">
+        <v>566</v>
+      </c>
+      <c r="F477" t="s">
+        <v>217</v>
+      </c>
+      <c r="G477" s="1">
+        <v>46029</v>
+      </c>
+      <c r="H477" t="s">
+        <v>134</v>
+      </c>
+      <c r="I477" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J477">
+        <v>5</v>
+      </c>
+      <c r="K477" t="s">
+        <v>221</v>
+      </c>
+      <c r="L477" t="s">
+        <v>1189</v>
+      </c>
+      <c r="M477" t="s">
+        <v>1186</v>
+      </c>
+      <c r="N477" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A478">
+        <v>373</v>
+      </c>
+      <c r="B478" t="s">
+        <v>13</v>
+      </c>
+      <c r="C478" t="s">
+        <v>50</v>
+      </c>
+      <c r="D478" t="s">
+        <v>15</v>
+      </c>
+      <c r="E478" t="s">
+        <v>566</v>
+      </c>
+      <c r="F478" t="s">
+        <v>217</v>
+      </c>
+      <c r="G478" s="1">
+        <v>46029</v>
+      </c>
+      <c r="H478" t="s">
+        <v>134</v>
+      </c>
+      <c r="I478" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J478">
+        <v>5</v>
+      </c>
+      <c r="K478" t="s">
+        <v>209</v>
+      </c>
+      <c r="L478" t="s">
+        <v>1190</v>
+      </c>
+      <c r="M478" t="s">
+        <v>1186</v>
+      </c>
+      <c r="N478" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A479">
+        <v>375</v>
+      </c>
+      <c r="B479" t="s">
+        <v>22</v>
+      </c>
+      <c r="C479" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D479" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E479" t="s">
+        <v>884</v>
+      </c>
+      <c r="F479" t="s">
+        <v>227</v>
+      </c>
+      <c r="G479" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H479" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I479" t="s">
+        <v>1195</v>
+      </c>
+      <c r="J479">
+        <v>5</v>
+      </c>
+      <c r="K479" t="s">
+        <v>209</v>
+      </c>
+      <c r="L479" t="s">
+        <v>1196</v>
+      </c>
+      <c r="M479" t="s">
+        <v>1197</v>
+      </c>
+      <c r="N479" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A480">
+        <v>377</v>
+      </c>
+      <c r="B480" t="s">
+        <v>13</v>
+      </c>
+      <c r="C480" t="s">
+        <v>50</v>
+      </c>
+      <c r="D480" t="s">
+        <v>15</v>
+      </c>
+      <c r="E480" t="s">
+        <v>583</v>
+      </c>
+      <c r="F480" t="s">
+        <v>217</v>
+      </c>
+      <c r="G480" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H480" t="s">
+        <v>134</v>
+      </c>
+      <c r="I480" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J480">
+        <v>5</v>
+      </c>
+      <c r="K480" t="s">
+        <v>221</v>
+      </c>
+      <c r="L480" t="s">
+        <v>1200</v>
+      </c>
+      <c r="M480" t="s">
+        <v>1186</v>
+      </c>
+      <c r="N480" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="481" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A481">
+        <v>377</v>
+      </c>
+      <c r="B481" t="s">
+        <v>13</v>
+      </c>
+      <c r="C481" t="s">
+        <v>50</v>
+      </c>
+      <c r="D481" t="s">
+        <v>15</v>
+      </c>
+      <c r="E481" t="s">
+        <v>583</v>
+      </c>
+      <c r="F481" t="s">
+        <v>217</v>
+      </c>
+      <c r="G481" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H481" t="s">
+        <v>134</v>
+      </c>
+      <c r="I481" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J481">
+        <v>5</v>
+      </c>
+      <c r="K481" t="s">
+        <v>209</v>
+      </c>
+      <c r="L481" t="s">
+        <v>1185</v>
+      </c>
+      <c r="M481" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="482" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A482">
+        <v>375</v>
+      </c>
+      <c r="B482" t="s">
+        <v>22</v>
+      </c>
+      <c r="C482" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D482" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E482" t="s">
+        <v>884</v>
+      </c>
+      <c r="F482" t="s">
+        <v>55</v>
+      </c>
+      <c r="G482" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H482" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I482" t="s">
+        <v>1195</v>
+      </c>
+      <c r="J482">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="483" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A483">
+        <v>374</v>
+      </c>
+      <c r="B483" t="s">
+        <v>67</v>
+      </c>
+      <c r="C483" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D483" t="s">
+        <v>69</v>
+      </c>
+      <c r="E483" t="s">
+        <v>147</v>
+      </c>
+      <c r="F483" t="s">
+        <v>17</v>
+      </c>
+      <c r="G483" s="1">
+        <v>46029</v>
+      </c>
+      <c r="H483" t="s">
+        <v>71</v>
+      </c>
+      <c r="I483" t="s">
+        <v>1203</v>
+      </c>
+      <c r="J483">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="484" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A484">
+        <v>376</v>
+      </c>
+      <c r="B484" t="s">
+        <v>67</v>
+      </c>
+      <c r="C484" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D484" t="s">
+        <v>63</v>
+      </c>
+      <c r="E484" t="s">
+        <v>903</v>
+      </c>
+      <c r="F484" t="s">
+        <v>17</v>
+      </c>
+      <c r="G484" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H484" t="s">
+        <v>479</v>
+      </c>
+      <c r="I484" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J484">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="485" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A485">
+        <v>376</v>
+      </c>
+      <c r="B485" t="s">
+        <v>67</v>
+      </c>
+      <c r="C485" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D485" t="s">
+        <v>63</v>
+      </c>
+      <c r="E485" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F485" t="s">
+        <v>17</v>
+      </c>
+      <c r="G485" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H485" t="s">
+        <v>479</v>
+      </c>
+      <c r="I485" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J485">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="486" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A486">
+        <v>376</v>
+      </c>
+      <c r="B486" t="s">
+        <v>67</v>
+      </c>
+      <c r="C486" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D486" t="s">
+        <v>63</v>
+      </c>
+      <c r="E486" t="s">
+        <v>64</v>
+      </c>
+      <c r="F486" t="s">
+        <v>17</v>
+      </c>
+      <c r="G486" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H486" t="s">
+        <v>479</v>
+      </c>
+      <c r="I486" t="s">
+        <v>1207</v>
+      </c>
+      <c r="J486">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="487" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A487">
+        <v>376</v>
+      </c>
+      <c r="B487" t="s">
+        <v>67</v>
+      </c>
+      <c r="C487" t="s">
+        <v>1204</v>
+      </c>
+      <c r="D487" t="s">
+        <v>63</v>
+      </c>
+      <c r="E487" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F487" t="s">
+        <v>17</v>
+      </c>
+      <c r="G487" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H487" t="s">
+        <v>479</v>
+      </c>
+      <c r="I487" t="s">
+        <v>1209</v>
+      </c>
+      <c r="J487">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="488" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A488">
+        <v>377</v>
+      </c>
+      <c r="B488" t="s">
+        <v>13</v>
+      </c>
+      <c r="C488" t="s">
+        <v>50</v>
+      </c>
+      <c r="D488" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E488" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F488" t="s">
+        <v>17</v>
+      </c>
+      <c r="G488" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H488" t="s">
+        <v>134</v>
+      </c>
+      <c r="I488" t="s">
+        <v>1211</v>
+      </c>
+      <c r="J488">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A489">
+        <v>377</v>
+      </c>
+      <c r="B489" t="s">
+        <v>13</v>
+      </c>
+      <c r="C489" t="s">
+        <v>50</v>
+      </c>
+      <c r="D489" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E489" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F489" t="s">
+        <v>17</v>
+      </c>
+      <c r="G489" s="1">
+        <v>46030</v>
+      </c>
+      <c r="H489" t="s">
+        <v>134</v>
+      </c>
+      <c r="I489" t="s">
+        <v>1213</v>
+      </c>
+      <c r="J489">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Tipos de trabajo/output/resumen_trabajos.xlsx
+++ b/Tipos de trabajo/output/resumen_trabajos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/Tipos de trabajo/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3399D3-5234-2C47-B7ED-BD82D57A553B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53CA0732-4EDE-CB45-8775-B109E42FF772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,8 +22,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="35" r:id="rId4"/>
+    <pivotCache cacheId="36" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27890,7 +27890,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{251B7304-8C5B-B84E-825B-578237745F65}" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{251B7304-8C5B-B84E-825B-578237745F65}" name="TablaDinámica2" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
   <location ref="R3:Z211" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="24">
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -28993,7 +28993,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC1700F9-4E18-744C-BA4A-04E48CEDB760}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC1700F9-4E18-744C-BA4A-04E48CEDB760}" name="TablaDinámica1" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="24">
     <pivotField dataField="1" showAll="0"/>
@@ -29205,7 +29205,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58C144FF-F8BA-0042-8CC8-638EF8B29700}" name="Resumen" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58C144FF-F8BA-0042-8CC8-638EF8B29700}" name="Resumen" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11">
   <location ref="A1:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0"/>
@@ -29564,7 +29564,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}" name="Tabla1" displayName="Tabla1" ref="A1:X517" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
-  <autoFilter ref="A1:X517" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}"/>
+  <autoFilter ref="A1:X517" xr:uid="{32CCDECC-D932-5D4F-9FF6-DAB914B6B73F}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="[Global Tórtolas] Pozo BN3"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N506">
     <sortCondition ref="G1:G506"/>
   </sortState>
@@ -32696,7 +32702,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>81</v>
       </c>
@@ -32734,7 +32740,7 @@
         <v>45894</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>81</v>
       </c>
@@ -32773,7 +32779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>81</v>
       </c>
@@ -32814,7 +32820,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>81</v>
       </c>
@@ -32855,7 +32861,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>81</v>
       </c>
@@ -32896,7 +32902,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>81</v>
       </c>
@@ -32937,7 +32943,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>81</v>
       </c>
@@ -32978,7 +32984,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>81</v>
       </c>
@@ -33019,7 +33025,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>78</v>
       </c>
@@ -33054,7 +33060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>76</v>
       </c>
@@ -33095,7 +33101,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>89</v>
       </c>
@@ -33136,7 +33142,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>89</v>
       </c>
@@ -33177,7 +33183,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>83</v>
       </c>
@@ -33209,7 +33215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>83</v>
       </c>
@@ -33247,7 +33253,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>83</v>
       </c>
@@ -33285,7 +33291,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>83</v>
       </c>
@@ -33323,7 +33329,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>83</v>
       </c>
@@ -33361,7 +33367,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>82</v>
       </c>
@@ -33402,7 +33408,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>88</v>
       </c>
@@ -33443,7 +33449,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>88</v>
       </c>
@@ -33484,7 +33490,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>87</v>
       </c>
@@ -33519,7 +33525,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>86</v>
       </c>
@@ -33560,7 +33566,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>86</v>
       </c>
@@ -33601,7 +33607,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>86</v>
       </c>
@@ -33642,7 +33648,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>86</v>
       </c>
@@ -33683,7 +33689,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>86</v>
       </c>
@@ -33724,7 +33730,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>86</v>
       </c>
@@ -33765,7 +33771,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>84</v>
       </c>
@@ -33806,7 +33812,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>84</v>
       </c>
@@ -33847,7 +33853,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>92</v>
       </c>
@@ -33882,7 +33888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>91</v>
       </c>
@@ -33917,7 +33923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>91</v>
       </c>
@@ -33958,7 +33964,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>91</v>
       </c>
@@ -33999,7 +34005,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>91</v>
       </c>
@@ -34040,7 +34046,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>91</v>
       </c>
@@ -34081,7 +34087,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>90</v>
       </c>
@@ -34122,7 +34128,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>98</v>
       </c>
@@ -34157,7 +34163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>93</v>
       </c>
@@ -34192,7 +34198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>93</v>
       </c>
@@ -34227,7 +34233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>93</v>
       </c>
@@ -34262,7 +34268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>93</v>
       </c>
@@ -34297,7 +34303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>93</v>
       </c>
@@ -34338,7 +34344,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>93</v>
       </c>
@@ -34379,7 +34385,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>103</v>
       </c>
@@ -34414,7 +34420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>99</v>
       </c>
@@ -34455,7 +34461,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>97</v>
       </c>
@@ -34490,7 +34496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>97</v>
       </c>
@@ -34525,7 +34531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>97</v>
       </c>
@@ -34566,7 +34572,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>96</v>
       </c>
@@ -34601,7 +34607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>96</v>
       </c>
@@ -34642,7 +34648,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>96</v>
       </c>
@@ -34683,7 +34689,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>115</v>
       </c>
@@ -34718,7 +34724,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>115</v>
       </c>
@@ -34753,7 +34759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>115</v>
       </c>
@@ -34788,7 +34794,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>102</v>
       </c>
@@ -34823,7 +34829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>101</v>
       </c>
@@ -34858,7 +34864,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>101</v>
       </c>
@@ -34893,7 +34899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>101</v>
       </c>
@@ -34928,7 +34934,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>101</v>
       </c>
@@ -34963,7 +34969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>101</v>
       </c>
@@ -34998,7 +35004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>101</v>
       </c>
@@ -35039,7 +35045,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>100</v>
       </c>
@@ -35074,7 +35080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>100</v>
       </c>
@@ -35109,7 +35115,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>100</v>
       </c>
@@ -35144,7 +35150,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>100</v>
       </c>
@@ -35179,7 +35185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>100</v>
       </c>
@@ -35214,7 +35220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>114</v>
       </c>
@@ -35249,7 +35255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>114</v>
       </c>
@@ -35284,7 +35290,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>106</v>
       </c>
@@ -35325,7 +35331,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>105</v>
       </c>
@@ -35360,7 +35366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>105</v>
       </c>
@@ -35395,7 +35401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>105</v>
       </c>
@@ -35436,7 +35442,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>104</v>
       </c>
@@ -35477,7 +35483,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>110</v>
       </c>
@@ -35512,7 +35518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>110</v>
       </c>
@@ -35547,7 +35553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>110</v>
       </c>
@@ -35582,7 +35588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>108</v>
       </c>
@@ -35623,7 +35629,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>108</v>
       </c>
@@ -35664,7 +35670,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>112</v>
       </c>
@@ -35699,7 +35705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>112</v>
       </c>
@@ -35734,7 +35740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>111</v>
       </c>
@@ -35769,7 +35775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>111</v>
       </c>
@@ -35804,7 +35810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>111</v>
       </c>
@@ -35839,7 +35845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>118</v>
       </c>
@@ -35874,7 +35880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>118</v>
       </c>
@@ -35909,7 +35915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>118</v>
       </c>
@@ -35950,7 +35956,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="304" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" ht="304" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>117</v>
       </c>
@@ -35985,7 +35991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>117</v>
       </c>
@@ -36026,7 +36032,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>117</v>
       </c>
@@ -36067,7 +36073,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>116</v>
       </c>
@@ -36108,7 +36114,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>116</v>
       </c>
@@ -36149,7 +36155,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>121</v>
       </c>
@@ -36190,7 +36196,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>121</v>
       </c>
@@ -36231,7 +36237,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>120</v>
       </c>
@@ -36272,7 +36278,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>119</v>
       </c>
@@ -36307,7 +36313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>119</v>
       </c>
@@ -36348,7 +36354,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>119</v>
       </c>
@@ -36389,7 +36395,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>119</v>
       </c>
@@ -36430,7 +36436,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>119</v>
       </c>
@@ -36477,7 +36483,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>119</v>
       </c>
@@ -36524,7 +36530,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>124</v>
       </c>
@@ -36571,7 +36577,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>124</v>
       </c>
@@ -36618,7 +36624,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>123</v>
       </c>
@@ -36659,7 +36665,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>123</v>
       </c>
@@ -36700,7 +36706,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>123</v>
       </c>
@@ -36741,7 +36747,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>122</v>
       </c>
@@ -36788,7 +36794,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>122</v>
       </c>
@@ -36835,7 +36841,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>122</v>
       </c>
@@ -36882,7 +36888,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>122</v>
       </c>
@@ -36929,7 +36935,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>122</v>
       </c>
@@ -36976,7 +36982,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>126</v>
       </c>
@@ -37017,7 +37023,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>126</v>
       </c>
@@ -37058,7 +37064,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>126</v>
       </c>
@@ -37099,7 +37105,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>125</v>
       </c>
@@ -37146,7 +37152,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>125</v>
       </c>
@@ -37193,7 +37199,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>129</v>
       </c>
@@ -37234,7 +37240,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>129</v>
       </c>
@@ -37275,7 +37281,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>129</v>
       </c>
@@ -37316,7 +37322,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>129</v>
       </c>
@@ -37357,7 +37363,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>129</v>
       </c>
@@ -37398,7 +37404,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>129</v>
       </c>
@@ -37439,7 +37445,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>133</v>
       </c>
@@ -37483,7 +37489,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>132</v>
       </c>
@@ -37524,7 +37530,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>130</v>
       </c>
@@ -37565,7 +37571,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>130</v>
       </c>
@@ -37606,7 +37612,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>136</v>
       </c>
@@ -37653,7 +37659,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>138</v>
       </c>
@@ -37694,7 +37700,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>139</v>
       </c>
@@ -37741,7 +37747,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>144</v>
       </c>
@@ -37788,7 +37794,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>143</v>
       </c>
@@ -37829,7 +37835,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>150</v>
       </c>
@@ -37876,7 +37882,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>148</v>
       </c>
@@ -37914,7 +37920,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>148</v>
       </c>
@@ -37952,7 +37958,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>148</v>
       </c>
@@ -37990,7 +37996,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>148</v>
       </c>
@@ -38028,7 +38034,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>148</v>
       </c>
@@ -38066,7 +38072,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>148</v>
       </c>
@@ -38104,7 +38110,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>154</v>
       </c>
@@ -38151,7 +38157,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>153</v>
       </c>
@@ -38192,7 +38198,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>153</v>
       </c>
@@ -38233,7 +38239,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>153</v>
       </c>
@@ -38274,7 +38280,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>161</v>
       </c>
@@ -38315,7 +38321,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>155</v>
       </c>
@@ -38356,7 +38362,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>155</v>
       </c>
@@ -38391,7 +38397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>162</v>
       </c>
@@ -38426,7 +38432,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>156</v>
       </c>
@@ -38461,7 +38467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>169</v>
       </c>
@@ -38496,7 +38502,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>167</v>
       </c>
@@ -38531,7 +38537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>164</v>
       </c>
@@ -38566,7 +38572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>164</v>
       </c>
@@ -38607,7 +38613,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>163</v>
       </c>
@@ -38642,7 +38648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>163</v>
       </c>
@@ -38677,7 +38683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>163</v>
       </c>
@@ -38712,7 +38718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>160</v>
       </c>
@@ -38747,7 +38753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>159</v>
       </c>
@@ -38782,7 +38788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>158</v>
       </c>
@@ -38817,7 +38823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:19" ht="176" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:19" ht="176" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>168</v>
       </c>
@@ -38849,7 +38855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:19" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>168</v>
       </c>
@@ -38881,7 +38887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>166</v>
       </c>
@@ -38916,7 +38922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>173</v>
       </c>
@@ -38957,7 +38963,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>172</v>
       </c>
@@ -38989,7 +38995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>172</v>
       </c>
@@ -39021,7 +39027,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>172</v>
       </c>
@@ -39053,7 +39059,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>171</v>
       </c>
@@ -39088,7 +39094,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>175</v>
       </c>
@@ -39123,7 +39129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>175</v>
       </c>
@@ -39158,7 +39164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>175</v>
       </c>
@@ -39193,7 +39199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>175</v>
       </c>
@@ -39228,7 +39234,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>178</v>
       </c>
@@ -39263,7 +39269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>176</v>
       </c>
@@ -39298,7 +39304,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>176</v>
       </c>
@@ -39333,7 +39339,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>176</v>
       </c>
@@ -39368,7 +39374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>182</v>
       </c>
@@ -39403,7 +39409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>182</v>
       </c>
@@ -39444,7 +39450,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>180</v>
       </c>
@@ -39479,7 +39485,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>180</v>
       </c>
@@ -39520,7 +39526,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>179</v>
       </c>
@@ -39555,7 +39561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>179</v>
       </c>
@@ -39596,7 +39602,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>187</v>
       </c>
@@ -39631,7 +39637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>187</v>
       </c>
@@ -39666,7 +39672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>187</v>
       </c>
@@ -39701,7 +39707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>187</v>
       </c>
@@ -39736,7 +39742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>185</v>
       </c>
@@ -39777,7 +39783,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>184</v>
       </c>
@@ -39812,7 +39818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>183</v>
       </c>
@@ -39847,7 +39853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>190</v>
       </c>
@@ -39900,7 +39906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>190</v>
       </c>
@@ -39953,7 +39959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>190</v>
       </c>
@@ -40012,7 +40018,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>190</v>
       </c>
@@ -40071,7 +40077,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>189</v>
       </c>
@@ -40130,7 +40136,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>188</v>
       </c>
@@ -40183,7 +40189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>188</v>
       </c>
@@ -40236,7 +40242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>188</v>
       </c>
@@ -40289,7 +40295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>188</v>
       </c>
@@ -40342,7 +40348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>188</v>
       </c>
@@ -40395,7 +40401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>192</v>
       </c>
@@ -40448,7 +40454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>191</v>
       </c>
@@ -40501,7 +40507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>191</v>
       </c>
@@ -40554,7 +40560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>191</v>
       </c>
@@ -40607,7 +40613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>191</v>
       </c>
@@ -40660,7 +40666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>195</v>
       </c>
@@ -40719,7 +40725,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>195</v>
       </c>
@@ -40778,7 +40784,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>194</v>
       </c>
@@ -40831,7 +40837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>194</v>
       </c>
@@ -40884,7 +40890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>194</v>
       </c>
@@ -40937,7 +40943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>194</v>
       </c>
@@ -40996,7 +41002,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>193</v>
       </c>
@@ -41055,7 +41061,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>193</v>
       </c>
@@ -41114,7 +41120,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>193</v>
       </c>
@@ -41173,7 +41179,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>200</v>
       </c>
@@ -41232,7 +41238,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>199</v>
       </c>
@@ -41285,7 +41291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>199</v>
       </c>
@@ -41344,7 +41350,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>199</v>
       </c>
@@ -41403,7 +41409,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>198</v>
       </c>
@@ -41456,7 +41462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>198</v>
       </c>
@@ -41509,7 +41515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>198</v>
       </c>
@@ -41562,7 +41568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>198</v>
       </c>
@@ -41615,7 +41621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>198</v>
       </c>
@@ -41668,7 +41674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>198</v>
       </c>
@@ -41721,7 +41727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>196</v>
       </c>
@@ -41774,7 +41780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>196</v>
       </c>
@@ -41827,7 +41833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>196</v>
       </c>
@@ -41880,7 +41886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>196</v>
       </c>
@@ -41933,7 +41939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>205</v>
       </c>
@@ -41986,7 +41992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>205</v>
       </c>
@@ -42039,7 +42045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>205</v>
       </c>
@@ -42098,7 +42104,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>205</v>
       </c>
@@ -42157,7 +42163,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>204</v>
       </c>
@@ -42216,7 +42222,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="230" spans="1:19" ht="304" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:19" ht="304" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>202</v>
       </c>
@@ -42269,7 +42275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>202</v>
       </c>
@@ -42328,7 +42334,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>202</v>
       </c>
@@ -42387,7 +42393,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>202</v>
       </c>
@@ -42446,7 +42452,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>201</v>
       </c>
@@ -42499,7 +42505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>201</v>
       </c>
@@ -42552,7 +42558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>201</v>
       </c>
@@ -42611,7 +42617,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>201</v>
       </c>
@@ -42670,7 +42676,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>209</v>
       </c>
@@ -42729,7 +42735,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>207</v>
       </c>
@@ -42782,7 +42788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>207</v>
       </c>
@@ -42841,7 +42847,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>206</v>
       </c>
@@ -42894,7 +42900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>206</v>
       </c>
@@ -42947,7 +42953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>214</v>
       </c>
@@ -43000,7 +43006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>213</v>
       </c>
@@ -43053,7 +43059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:21" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>212</v>
       </c>
@@ -43112,7 +43118,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>210</v>
       </c>
@@ -43171,7 +43177,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>217</v>
       </c>
@@ -43224,7 +43230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>217</v>
       </c>
@@ -43277,7 +43283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>217</v>
       </c>
@@ -43330,7 +43336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>217</v>
       </c>
@@ -43383,7 +43389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>217</v>
       </c>
@@ -43436,7 +43442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>217</v>
       </c>
@@ -43489,7 +43495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>216</v>
       </c>
@@ -43542,7 +43548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>216</v>
       </c>
@@ -43601,7 +43607,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="255" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:21" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>220</v>
       </c>
@@ -43660,7 +43666,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>219</v>
       </c>
@@ -43719,7 +43725,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>219</v>
       </c>
@@ -43775,7 +43781,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>219</v>
       </c>
@@ -43834,7 +43840,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>219</v>
       </c>
@@ -43893,7 +43899,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>224</v>
       </c>
@@ -43952,7 +43958,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>224</v>
       </c>
@@ -44017,7 +44023,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>223</v>
       </c>
@@ -44076,7 +44082,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>223</v>
       </c>
@@ -44135,7 +44141,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>223</v>
       </c>
@@ -44194,7 +44200,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>223</v>
       </c>
@@ -44253,7 +44259,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>226</v>
       </c>
@@ -44318,7 +44324,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>229</v>
       </c>
@@ -44383,7 +44389,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>233</v>
       </c>
@@ -44442,7 +44448,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>233</v>
       </c>
@@ -44501,7 +44507,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>233</v>
       </c>
@@ -44560,7 +44566,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>233</v>
       </c>
@@ -44619,7 +44625,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:21" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>231</v>
       </c>
@@ -44678,7 +44684,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>237</v>
       </c>
@@ -44743,7 +44749,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>237</v>
       </c>
@@ -44808,7 +44814,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>236</v>
       </c>
@@ -44867,7 +44873,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>236</v>
       </c>
@@ -44926,7 +44932,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>234</v>
       </c>
@@ -44985,7 +44991,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>234</v>
       </c>
@@ -45044,7 +45050,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>240</v>
       </c>
@@ -45103,7 +45109,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>240</v>
       </c>
@@ -45162,7 +45168,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="281" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>242</v>
       </c>
@@ -45221,7 +45227,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="282" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>242</v>
       </c>
@@ -45280,7 +45286,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="283" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>242</v>
       </c>
@@ -45339,7 +45345,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="284" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>242</v>
       </c>
@@ -45398,7 +45404,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>242</v>
       </c>
@@ -45457,7 +45463,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>241</v>
       </c>
@@ -45522,7 +45528,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="287" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>241</v>
       </c>
@@ -45587,7 +45593,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="288" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>241</v>
       </c>
@@ -45652,7 +45658,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="289" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>247</v>
       </c>
@@ -45711,7 +45717,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="290" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>244</v>
       </c>
@@ -45770,7 +45776,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="291" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>244</v>
       </c>
@@ -45829,7 +45835,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>244</v>
       </c>
@@ -45894,7 +45900,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="293" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>248</v>
       </c>
@@ -45953,7 +45959,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="294" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>246</v>
       </c>
@@ -46012,7 +46018,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="295" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>246</v>
       </c>
@@ -46071,7 +46077,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="296" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>245</v>
       </c>
@@ -46136,7 +46142,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="297" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>249</v>
       </c>
@@ -46195,7 +46201,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="298" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>253</v>
       </c>
@@ -46254,7 +46260,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="299" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>253</v>
       </c>
@@ -46313,7 +46319,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="300" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>255</v>
       </c>
@@ -46372,7 +46378,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="301" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>255</v>
       </c>
@@ -46431,7 +46437,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="302" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>254</v>
       </c>
@@ -46490,7 +46496,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="303" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>258</v>
       </c>
@@ -46549,7 +46555,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="304" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>258</v>
       </c>
@@ -46608,7 +46614,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="305" spans="1:21" ht="128" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:21" ht="128" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>258</v>
       </c>
@@ -46673,7 +46679,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="306" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>257</v>
       </c>
@@ -46732,7 +46738,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="307" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>257</v>
       </c>
@@ -46791,7 +46797,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="308" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>257</v>
       </c>
@@ -46856,7 +46862,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="309" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>257</v>
       </c>
@@ -46921,7 +46927,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="310" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>260</v>
       </c>
@@ -46974,7 +46980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>260</v>
       </c>
@@ -47033,7 +47039,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="312" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>260</v>
       </c>
@@ -47092,7 +47098,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="313" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>263</v>
       </c>
@@ -47151,7 +47157,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="314" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>262</v>
       </c>
@@ -47204,7 +47210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:21" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>262</v>
       </c>
@@ -47257,7 +47263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>270</v>
       </c>
@@ -47316,7 +47322,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="317" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>267</v>
       </c>
@@ -47369,7 +47375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>267</v>
       </c>
@@ -47422,7 +47428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:21" ht="192" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:21" ht="192" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>266</v>
       </c>
@@ -47475,7 +47481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>266</v>
       </c>
@@ -47528,7 +47534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>266</v>
       </c>
@@ -47581,7 +47587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>266</v>
       </c>
@@ -47634,7 +47640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>268</v>
       </c>
@@ -47687,7 +47693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>272</v>
       </c>
@@ -47740,7 +47746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>272</v>
       </c>
@@ -47793,7 +47799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>272</v>
       </c>
@@ -47846,7 +47852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>272</v>
       </c>
@@ -47899,7 +47905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>272</v>
       </c>
@@ -47952,7 +47958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>276</v>
       </c>
@@ -48005,7 +48011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>276</v>
       </c>
@@ -48058,7 +48064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>276</v>
       </c>
@@ -48111,7 +48117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>274</v>
       </c>
@@ -48164,7 +48170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>280</v>
       </c>
@@ -48223,7 +48229,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="334" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>280</v>
       </c>
@@ -48282,7 +48288,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="335" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>280</v>
       </c>
@@ -48341,7 +48347,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="336" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>278</v>
       </c>
@@ -48394,7 +48400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>278</v>
       </c>
@@ -48447,7 +48453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>278</v>
       </c>
@@ -48500,7 +48506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>277</v>
       </c>
@@ -48559,7 +48565,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="340" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:19" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>283</v>
       </c>
@@ -48612,7 +48618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>283</v>
       </c>
@@ -48665,7 +48671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>283</v>
       </c>
@@ -48718,7 +48724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>282</v>
       </c>
@@ -48777,7 +48783,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="344" spans="1:19" ht="304" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:19" ht="304" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>281</v>
       </c>
@@ -48830,7 +48836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>281</v>
       </c>
@@ -48889,7 +48895,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="346" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>281</v>
       </c>
@@ -48948,7 +48954,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="347" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>281</v>
       </c>
@@ -49007,7 +49013,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="348" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>281</v>
       </c>
@@ -49066,7 +49072,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="349" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>291</v>
       </c>
@@ -49119,7 +49125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>291</v>
       </c>
@@ -49178,7 +49184,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="351" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>291</v>
       </c>
@@ -49237,7 +49243,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="352" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>286</v>
       </c>
@@ -49296,7 +49302,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="353" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>284</v>
       </c>
@@ -49402,7 +49408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>289</v>
       </c>
@@ -49461,7 +49467,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="356" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>288</v>
       </c>
@@ -49514,7 +49520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>288</v>
       </c>
@@ -49567,7 +49573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>288</v>
       </c>
@@ -49620,7 +49626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>288</v>
       </c>
@@ -49673,7 +49679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>288</v>
       </c>
@@ -49726,7 +49732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>288</v>
       </c>
@@ -49779,7 +49785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>287</v>
       </c>
@@ -49832,7 +49838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>310</v>
       </c>
@@ -49885,7 +49891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>310</v>
       </c>
@@ -49938,7 +49944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>293</v>
       </c>
@@ -49997,7 +50003,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>293</v>
       </c>
@@ -50056,7 +50062,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>293</v>
       </c>
@@ -50115,7 +50121,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>293</v>
       </c>
@@ -50174,7 +50180,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>293</v>
       </c>
@@ -50233,7 +50239,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>293</v>
       </c>
@@ -50292,7 +50298,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>292</v>
       </c>
@@ -50345,7 +50351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>292</v>
       </c>
@@ -50398,7 +50404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>292</v>
       </c>
@@ -50451,7 +50457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>292</v>
       </c>
@@ -50504,7 +50510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>290</v>
       </c>
@@ -50557,7 +50563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>290</v>
       </c>
@@ -50610,7 +50616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>317</v>
       </c>
@@ -50663,7 +50669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>299</v>
       </c>
@@ -50716,7 +50722,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>299</v>
       </c>
@@ -50769,7 +50775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>299</v>
       </c>
@@ -50822,7 +50828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>311</v>
       </c>
@@ -50875,7 +50881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="382" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>309</v>
       </c>
@@ -50928,7 +50934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="383" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>302</v>
       </c>
@@ -50981,7 +50987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>302</v>
       </c>
@@ -51034,7 +51040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="385" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>302</v>
       </c>
@@ -51087,7 +51093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="386" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>302</v>
       </c>
@@ -51140,7 +51146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="387" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>302</v>
       </c>
@@ -51193,7 +51199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:19" ht="224" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:19" ht="224" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>300</v>
       </c>
@@ -51246,7 +51252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:19" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:19" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>300</v>
       </c>
@@ -51299,7 +51305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>305</v>
       </c>
@@ -51352,7 +51358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>304</v>
       </c>
@@ -51411,7 +51417,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="392" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>308</v>
       </c>
@@ -51464,7 +51470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="393" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>306</v>
       </c>
@@ -51517,7 +51523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="394" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>306</v>
       </c>
@@ -51570,7 +51576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="395" spans="1:19" ht="380" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:19" ht="380" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>314</v>
       </c>
@@ -51623,7 +51629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="396" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>314</v>
       </c>
@@ -51676,7 +51682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="397" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>313</v>
       </c>
@@ -51729,7 +51735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="398" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>313</v>
       </c>
@@ -51782,7 +51788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>313</v>
       </c>
@@ -51835,7 +51841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="400" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>313</v>
       </c>
@@ -51888,7 +51894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="401" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>312</v>
       </c>
@@ -51941,7 +51947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="402" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>312</v>
       </c>
@@ -51994,7 +52000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="403" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>312</v>
       </c>
@@ -52047,7 +52053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="404" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>312</v>
       </c>
@@ -52100,7 +52106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="405" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>315</v>
       </c>
@@ -52153,7 +52159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="406" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>315</v>
       </c>
@@ -52206,7 +52212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="407" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>315</v>
       </c>
@@ -52259,7 +52265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>318</v>
       </c>
@@ -52312,7 +52318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>318</v>
       </c>
@@ -52365,7 +52371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:17" ht="240" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:17" ht="240" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>327</v>
       </c>
@@ -52418,7 +52424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>327</v>
       </c>
@@ -52471,7 +52477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>322</v>
       </c>
@@ -52524,7 +52530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="413" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:17" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>321</v>
       </c>
@@ -52577,7 +52583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="414" spans="1:17" ht="256" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:17" ht="256" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>321</v>
       </c>
@@ -52630,7 +52636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="415" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>320</v>
       </c>
@@ -52683,7 +52689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="416" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>326</v>
       </c>
@@ -52736,7 +52742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>326</v>
       </c>
@@ -52795,7 +52801,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="418" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>326</v>
       </c>
@@ -52854,7 +52860,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="419" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>326</v>
       </c>
@@ -52913,7 +52919,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="420" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>325</v>
       </c>
@@ -53025,7 +53031,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="422" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>330</v>
       </c>
@@ -53078,7 +53084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="423" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>329</v>
       </c>
@@ -53137,7 +53143,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="424" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>334</v>
       </c>
@@ -53196,7 +53202,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="425" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>338</v>
       </c>
@@ -53252,7 +53258,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="426" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>337</v>
       </c>
@@ -53314,7 +53320,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="427" spans="1:21" ht="288" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:21" ht="288" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>336</v>
       </c>
@@ -53373,7 +53379,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="428" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>340</v>
       </c>
@@ -53432,7 +53438,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="429" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>339</v>
       </c>
@@ -53488,7 +53494,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="430" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>339</v>
       </c>
@@ -53547,7 +53553,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="431" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>342</v>
       </c>
@@ -53603,7 +53609,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="432" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>342</v>
       </c>
@@ -53659,7 +53665,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="433" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>341</v>
       </c>
@@ -53715,7 +53721,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="434" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>347</v>
       </c>
@@ -53771,7 +53777,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="435" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>345</v>
       </c>
@@ -53827,7 +53833,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="436" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>345</v>
       </c>
@@ -53886,7 +53892,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="437" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>344</v>
       </c>
@@ -53945,7 +53951,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="438" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>351</v>
       </c>
@@ -54004,7 +54010,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="439" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>351</v>
       </c>
@@ -54060,7 +54066,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="440" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>349</v>
       </c>
@@ -54116,7 +54122,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="441" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>348</v>
       </c>
@@ -54172,7 +54178,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="442" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>356</v>
       </c>
@@ -54228,7 +54234,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="443" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>353</v>
       </c>
@@ -54287,7 +54293,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="444" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>355</v>
       </c>
@@ -54346,7 +54352,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="445" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>359</v>
       </c>
@@ -54411,7 +54417,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="446" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>357</v>
       </c>
@@ -54467,7 +54473,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="447" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>357</v>
       </c>
@@ -54526,7 +54532,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="448" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>357</v>
       </c>
@@ -54585,7 +54591,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="449" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>362</v>
       </c>
@@ -54647,7 +54653,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="450" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>361</v>
       </c>
@@ -54706,7 +54712,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="451" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>361</v>
       </c>
@@ -54762,7 +54768,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="452" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>365</v>
       </c>
@@ -54818,7 +54824,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="453" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>365</v>
       </c>
@@ -54874,7 +54880,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="454" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>365</v>
       </c>
@@ -54933,7 +54939,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="455" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>368</v>
       </c>
@@ -54992,7 +54998,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="456" spans="1:21" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:21" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>368</v>
       </c>
@@ -55048,7 +55054,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="457" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>366</v>
       </c>
@@ -55113,7 +55119,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="458" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>382</v>
       </c>
@@ -55178,7 +55184,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="459" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>372</v>
       </c>
@@ -55237,7 +55243,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="460" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>372</v>
       </c>
@@ -55296,7 +55302,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="461" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>372</v>
       </c>
@@ -55352,7 +55358,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="462" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>372</v>
       </c>
@@ -55417,7 +55423,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="463" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>372</v>
       </c>
@@ -55479,7 +55485,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="464" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>370</v>
       </c>
@@ -55544,7 +55550,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="465" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>370</v>
       </c>
@@ -55609,7 +55615,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="466" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>370</v>
       </c>
@@ -55671,7 +55677,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="467" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>369</v>
       </c>
@@ -55730,7 +55736,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="468" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>392</v>
       </c>
@@ -55789,7 +55795,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="469" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>391</v>
       </c>
@@ -55848,7 +55854,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="470" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>391</v>
       </c>
@@ -55907,7 +55913,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="471" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>391</v>
       </c>
@@ -55966,7 +55972,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="472" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>391</v>
       </c>
@@ -56025,7 +56031,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="473" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>374</v>
       </c>
@@ -56084,7 +56090,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="474" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>373</v>
       </c>
@@ -56143,7 +56149,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="475" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>373</v>
       </c>
@@ -56208,7 +56214,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="476" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>373</v>
       </c>
@@ -56267,7 +56273,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="477" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>377</v>
       </c>
@@ -56320,7 +56326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="478" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>377</v>
       </c>
@@ -56373,7 +56379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>377</v>
       </c>
@@ -56432,7 +56438,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="480" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>377</v>
       </c>
@@ -56544,7 +56550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>376</v>
       </c>
@@ -56597,7 +56603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="483" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>376</v>
       </c>
@@ -56650,7 +56656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="484" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>376</v>
       </c>
@@ -56703,7 +56709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>375</v>
       </c>
@@ -56756,7 +56762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="486" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>375</v>
       </c>
@@ -56815,7 +56821,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="487" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>383</v>
       </c>
@@ -56880,7 +56886,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="488" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>383</v>
       </c>
@@ -56945,7 +56951,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="489" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>381</v>
       </c>
@@ -57007,7 +57013,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="490" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>381</v>
       </c>
@@ -57072,7 +57078,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="491" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>381</v>
       </c>
@@ -57134,7 +57140,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="492" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>381</v>
       </c>
@@ -57196,7 +57202,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="493" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>379</v>
       </c>
@@ -57261,7 +57267,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="494" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>379</v>
       </c>
@@ -57326,7 +57332,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="495" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>379</v>
       </c>
@@ -57391,7 +57397,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="496" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>387</v>
       </c>
@@ -57450,7 +57456,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="497" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>387</v>
       </c>
@@ -57515,7 +57521,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="498" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>385</v>
       </c>
@@ -57571,7 +57577,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="499" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>385</v>
       </c>
@@ -57630,7 +57636,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="500" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>385</v>
       </c>
@@ -57689,7 +57695,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="501" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>385</v>
       </c>
@@ -57754,7 +57760,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="502" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>385</v>
       </c>
@@ -57819,7 +57825,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="503" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503">
         <v>385</v>
       </c>
@@ -57884,7 +57890,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="504" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504">
         <v>385</v>
       </c>
@@ -57949,7 +57955,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="505" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505">
         <v>390</v>
       </c>
@@ -58008,7 +58014,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="506" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506">
         <v>389</v>
       </c>
@@ -58067,7 +58073,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="507" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507">
         <v>389</v>
       </c>
@@ -58123,7 +58129,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="508" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508">
         <v>386</v>
       </c>
@@ -58188,7 +58194,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="509" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509">
         <v>386</v>
       </c>
@@ -58253,7 +58259,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="510" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510">
         <v>386</v>
       </c>
@@ -58318,7 +58324,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="511" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511">
         <v>396</v>
       </c>
@@ -58383,7 +58389,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="512" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512">
         <v>396</v>
       </c>
@@ -58448,7 +58454,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="513" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513">
         <v>396</v>
       </c>
@@ -58513,7 +58519,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="514" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514">
         <v>395</v>
       </c>
@@ -58578,7 +58584,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="515" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515">
         <v>395</v>
       </c>
@@ -58643,7 +58649,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="516" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516">
         <v>395</v>
       </c>
@@ -58708,7 +58714,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="517" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517">
         <v>395</v>
       </c>
